--- a/salidas/empresas/COP.xlsx
+++ b/salidas/empresas/COP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>24.71615028381348</v>
+        <v>24.71616172790527</v>
       </c>
       <c r="C2" t="n">
         <v>49.32188034057617</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>23.43121719360352</v>
+        <v>23.43121147155762</v>
       </c>
       <c r="C3" t="n">
         <v>46.47081756591797</v>
@@ -520,7 +532,7 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>25.71436882019043</v>
+        <v>25.7143611907959</v>
       </c>
       <c r="C5" t="n">
         <v>50.99897766113281</v>
@@ -558,7 +570,7 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>25.33137130737305</v>
+        <v>25.33137512207031</v>
       </c>
       <c r="C7" t="n">
         <v>49.95460510253906</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>26.67353630065918</v>
+        <v>26.67356872558594</v>
       </c>
       <c r="C8" t="n">
         <v>52.32540893554688</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>24.64894866943359</v>
+        <v>24.64893531799316</v>
       </c>
       <c r="C9" t="n">
         <v>48.35374069213867</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>23.13340377807617</v>
+        <v>23.13339805603027</v>
       </c>
       <c r="C10" t="n">
         <v>45.38070678710938</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>23.54558372497559</v>
+        <v>23.54559135437012</v>
       </c>
       <c r="C11" t="n">
         <v>45.92194747924805</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>26.30508041381836</v>
+        <v>26.30507278442383</v>
       </c>
       <c r="C12" t="n">
         <v>51.30390548706055</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>28.12258911132812</v>
+        <v>28.12259674072266</v>
       </c>
       <c r="C13" t="n">
         <v>54.84867477416992</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>25.95720672607422</v>
+        <v>25.95720481872559</v>
       </c>
       <c r="C14" t="n">
         <v>50.62544250488281</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>25.68729209899902</v>
+        <v>25.68728828430176</v>
       </c>
       <c r="C15" t="n">
         <v>49.79451751708984</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>26.87884140014648</v>
+        <v>26.87883949279785</v>
       </c>
       <c r="C16" t="n">
         <v>52.10433578491211</v>
@@ -767,7 +779,7 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>30.62433052062988</v>
+        <v>30.62434005737305</v>
       </c>
       <c r="C18" t="n">
         <v>59.02617263793945</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>31.04753684997559</v>
+        <v>31.04752540588379</v>
       </c>
       <c r="C19" t="n">
         <v>59.84185028076172</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>32.13405609130859</v>
+        <v>32.13406372070312</v>
       </c>
       <c r="C20" t="n">
         <v>61.62567138671875</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>32.55143356323242</v>
+        <v>32.55144500732422</v>
       </c>
       <c r="C21" t="n">
         <v>62.42610168457031</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>34.88875198364258</v>
+        <v>34.88875961303711</v>
       </c>
       <c r="C22" t="n">
         <v>66.90852355957031</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>33.93582534790039</v>
+        <v>33.93584060668945</v>
       </c>
       <c r="C23" t="n">
         <v>64.76641845703125</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>31.97061920166016</v>
+        <v>31.97061538696289</v>
       </c>
       <c r="C24" t="n">
         <v>61.01581573486328</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>35.26993179321289</v>
+        <v>35.26993942260742</v>
       </c>
       <c r="C25" t="n">
         <v>67.31255340576172</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>31.99857902526855</v>
+        <v>31.99858474731445</v>
       </c>
       <c r="C26" t="n">
         <v>61.06917953491211</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>33.228515625</v>
+        <v>33.2285041809082</v>
       </c>
       <c r="C27" t="n">
         <v>63.05120468139648</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>30.61714172363281</v>
+        <v>30.61714363098145</v>
       </c>
       <c r="C28" t="n">
         <v>58.09614562988281</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>34.61050796508789</v>
+        <v>34.61050033569336</v>
       </c>
       <c r="C29" t="n">
         <v>65.67356872558594</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>37.59297943115234</v>
+        <v>37.59299087524414</v>
       </c>
       <c r="C30" t="n">
         <v>70.97167205810547</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>38.11387634277344</v>
+        <v>38.11387252807617</v>
       </c>
       <c r="C31" t="n">
         <v>71.95506286621094</v>
@@ -1052,7 +1064,7 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>33.50830459594727</v>
+        <v>33.50830078125</v>
       </c>
       <c r="C33" t="n">
         <v>62.89873886108398</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>29.74771118164062</v>
+        <v>29.74771499633789</v>
       </c>
       <c r="C34" t="n">
         <v>55.83968734741211</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>21.32167816162109</v>
+        <v>21.32167053222656</v>
       </c>
       <c r="C35" t="n">
         <v>39.6480827331543</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>21.5307445526123</v>
+        <v>21.53074645996094</v>
       </c>
       <c r="C36" t="n">
         <v>40.036865234375</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>21.23558235168457</v>
+        <v>21.2355842590332</v>
       </c>
       <c r="C37" t="n">
         <v>39.48799896240234</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>19.48507690429688</v>
+        <v>19.48508071899414</v>
       </c>
       <c r="C38" t="n">
         <v>36.23290634155273</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>15.48392581939697</v>
+        <v>15.48392677307129</v>
       </c>
       <c r="C39" t="n">
         <v>28.4725227355957</v>
@@ -1204,7 +1216,7 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
@@ -1223,7 +1235,7 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
@@ -1242,7 +1254,7 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
@@ -1261,7 +1273,7 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>18.50048065185547</v>
+        <v>18.50048446655273</v>
       </c>
       <c r="C44" t="n">
         <v>33.32085800170898</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>19.05917358398438</v>
+        <v>19.05917739868164</v>
       </c>
       <c r="C45" t="n">
         <v>34.32711410522461</v>
@@ -1324,11 +1336,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>19.11420249938965</v>
+        <v>19.11420631408691</v>
       </c>
       <c r="C46" t="n">
         <v>34.42621612548828</v>
@@ -1349,11 +1361,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>21.44757461547852</v>
+        <v>21.44757270812988</v>
       </c>
       <c r="C47" t="n">
         <v>38.25304412841797</v>
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>22.12716865539551</v>
+        <v>22.12716484069824</v>
       </c>
       <c r="C48" t="n">
         <v>39.46512985229492</v>
@@ -1399,7 +1411,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>20.51581382751465</v>
+        <v>20.51581954956055</v>
       </c>
       <c r="C50" t="n">
         <v>36.59119415283203</v>
@@ -1449,11 +1461,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>20.72601890563965</v>
+        <v>20.72602653503418</v>
       </c>
       <c r="C51" t="n">
         <v>36.59119415283203</v>
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>22.09479522705078</v>
+        <v>22.09480285644531</v>
       </c>
       <c r="C52" t="n">
         <v>39.00773620605469</v>
@@ -1499,11 +1511,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>25.55777359008789</v>
+        <v>25.55777168273926</v>
       </c>
       <c r="C53" t="n">
         <v>45.12151718139648</v>
@@ -1524,11 +1536,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>22.6235466003418</v>
+        <v>22.62354278564453</v>
       </c>
       <c r="C54" t="n">
         <v>39.53373718261719</v>
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>21.4151611328125</v>
+        <v>21.41514587402344</v>
       </c>
       <c r="C55" t="n">
         <v>37.422119140625</v>
@@ -1574,11 +1586,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>24.33518028259277</v>
+        <v>24.33518409729004</v>
       </c>
       <c r="C56" t="n">
         <v>42.09511947631836</v>
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>23.10563278198242</v>
+        <v>23.10563087463379</v>
       </c>
       <c r="C57" t="n">
         <v>39.96825790405273</v>
@@ -1624,11 +1636,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>25.30912017822266</v>
+        <v>25.30911445617676</v>
       </c>
       <c r="C58" t="n">
         <v>43.77983856201172</v>
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>26.40955543518066</v>
+        <v>26.40954780578613</v>
       </c>
       <c r="C59" t="n">
         <v>45.27397918701172</v>
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>26.75640296936035</v>
+        <v>26.75640678405762</v>
       </c>
       <c r="C60" t="n">
         <v>45.86858749389648</v>
@@ -1699,11 +1711,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>30.28271102905273</v>
+        <v>30.28271293640137</v>
       </c>
       <c r="C61" t="n">
         <v>51.91375732421875</v>
@@ -1724,11 +1736,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>31.7768383026123</v>
+        <v>31.77685356140137</v>
       </c>
       <c r="C62" t="n">
         <v>54.47513961791992</v>
@@ -1749,11 +1761,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>34.93487167358398</v>
+        <v>34.93486785888672</v>
       </c>
       <c r="C63" t="n">
         <v>59.36159133911133</v>
@@ -1778,7 +1790,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
@@ -1807,11 +1819,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>35.39249420166016</v>
+        <v>35.39247894287109</v>
       </c>
       <c r="C65" t="n">
         <v>60.13915252685547</v>
@@ -1836,11 +1848,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>33.14921569824219</v>
+        <v>33.14921951293945</v>
       </c>
       <c r="C66" t="n">
         <v>55.81681823730469</v>
@@ -1865,11 +1877,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>34.04112243652344</v>
+        <v>34.04111480712891</v>
       </c>
       <c r="C67" t="n">
         <v>57.31858062744141</v>
@@ -1894,7 +1906,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
@@ -1923,11 +1935,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>31.09085273742676</v>
+        <v>31.09083938598633</v>
       </c>
       <c r="C69" t="n">
         <v>51.89088821411133</v>
@@ -1952,11 +1964,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>28.92127990722656</v>
+        <v>28.92128372192383</v>
       </c>
       <c r="C70" t="n">
         <v>48.26988220214844</v>
@@ -1981,11 +1993,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>32.125</v>
+        <v>32.1249885559082</v>
       </c>
       <c r="C71" t="n">
         <v>53.0953483581543</v>
@@ -2010,7 +2022,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
@@ -2039,11 +2051,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>33.61016845703125</v>
+        <v>33.61017227172852</v>
       </c>
       <c r="C73" t="n">
         <v>55.55000686645508</v>
@@ -2068,7 +2080,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
@@ -2097,11 +2109,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>35.62765502929688</v>
+        <v>35.62765121459961</v>
       </c>
       <c r="C75" t="n">
         <v>58.35533142089844</v>
@@ -2126,11 +2138,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>35.37632751464844</v>
+        <v>35.37633514404297</v>
       </c>
       <c r="C76" t="n">
         <v>57.94368362426758</v>
@@ -2155,11 +2167,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>33.33780288696289</v>
+        <v>33.33781433105469</v>
       </c>
       <c r="C77" t="n">
         <v>54.604736328125</v>
@@ -2184,11 +2196,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>32.2520751953125</v>
+        <v>32.2520637512207</v>
       </c>
       <c r="C78" t="n">
         <v>52.15999984741211</v>
@@ -2213,11 +2225,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>34.55225372314453</v>
+        <v>34.55226898193359</v>
       </c>
       <c r="C79" t="n">
         <v>55.88000106811523</v>
@@ -2242,11 +2254,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>34.05781936645508</v>
+        <v>34.05781173706055</v>
       </c>
       <c r="C80" t="n">
         <v>54.43999862670898</v>
@@ -2271,7 +2283,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
@@ -2300,11 +2312,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>35.77196502685547</v>
+        <v>35.77195739746094</v>
       </c>
       <c r="C82" t="n">
         <v>57.18000030517578</v>
@@ -2329,7 +2341,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
@@ -2358,11 +2370,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>36.03734970092773</v>
+        <v>36.0373420715332</v>
       </c>
       <c r="C84" t="n">
         <v>56.93999862670898</v>
@@ -2387,11 +2399,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>36.70190048217773</v>
+        <v>36.70188522338867</v>
       </c>
       <c r="C85" t="n">
         <v>57.9900016784668</v>
@@ -2416,7 +2428,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
@@ -2445,11 +2457,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>37.09429550170898</v>
+        <v>37.09428787231445</v>
       </c>
       <c r="C87" t="n">
         <v>57.95000076293945</v>
@@ -2474,11 +2486,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>38.47052383422852</v>
+        <v>38.47051620483398</v>
       </c>
       <c r="C88" t="n">
         <v>60.09999847412109</v>
@@ -2503,11 +2515,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>38.69456481933594</v>
+        <v>38.6945686340332</v>
       </c>
       <c r="C89" t="n">
         <v>60.45000076293945</v>
@@ -2532,11 +2544,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>39.67138290405273</v>
+        <v>39.67140197753906</v>
       </c>
       <c r="C90" t="n">
         <v>61.34000015258789</v>
@@ -2561,11 +2573,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>39.12813186645508</v>
+        <v>39.12812805175781</v>
       </c>
       <c r="C91" t="n">
         <v>60.5</v>
@@ -2590,11 +2602,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>42.39413070678711</v>
+        <v>42.39413452148438</v>
       </c>
       <c r="C92" t="n">
         <v>64.86000061035156</v>
@@ -2619,11 +2631,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>43.33536148071289</v>
+        <v>43.33535385131836</v>
       </c>
       <c r="C93" t="n">
         <v>66.30000305175781</v>
@@ -2648,7 +2660,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
@@ -2677,11 +2689,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>48.40908813476562</v>
+        <v>48.40909194946289</v>
       </c>
       <c r="C95" t="n">
         <v>73.33000183105469</v>
@@ -2706,11 +2718,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>48.0592041015625</v>
+        <v>48.0591926574707</v>
       </c>
       <c r="C96" t="n">
         <v>72.80000305175781</v>
@@ -2735,11 +2747,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>46.63986968994141</v>
+        <v>46.63987731933594</v>
       </c>
       <c r="C97" t="n">
         <v>70.65000152587891</v>
@@ -2764,11 +2776,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>42.87699890136719</v>
+        <v>42.87699127197266</v>
       </c>
       <c r="C98" t="n">
         <v>64.94999694824219</v>
@@ -2793,11 +2805,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>44.36963653564453</v>
+        <v>44.36965179443359</v>
       </c>
       <c r="C99" t="n">
         <v>66.5</v>
@@ -2822,11 +2834,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>46.93840789794922</v>
+        <v>46.93841934204102</v>
       </c>
       <c r="C100" t="n">
         <v>70.34999847412109</v>
@@ -2851,11 +2863,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>49.58059692382812</v>
+        <v>49.58058166503906</v>
       </c>
       <c r="C101" t="n">
         <v>74.30999755859375</v>
@@ -2880,11 +2892,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>53.80972290039062</v>
+        <v>53.80974197387695</v>
       </c>
       <c r="C102" t="n">
         <v>79.94000244140625</v>
@@ -2909,11 +2921,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>57.70711135864258</v>
+        <v>57.70710372924805</v>
       </c>
       <c r="C103" t="n">
         <v>85.73000335693359</v>
@@ -2938,11 +2950,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>56.00451278686523</v>
+        <v>56.0045166015625</v>
       </c>
       <c r="C104" t="n">
         <v>82.5</v>
@@ -2967,11 +2979,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>55.1356201171875</v>
+        <v>55.13560104370117</v>
       </c>
       <c r="C105" t="n">
         <v>81.22000122070312</v>
@@ -2996,11 +3008,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>51.94504165649414</v>
+        <v>51.94506072998047</v>
       </c>
       <c r="C106" t="n">
         <v>76.51999664306641</v>
@@ -3025,7 +3037,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
@@ -3054,11 +3066,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>45.29478073120117</v>
+        <v>45.29479217529297</v>
       </c>
       <c r="C108" t="n">
         <v>66.06999969482422</v>
@@ -3083,11 +3095,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>47.34460830688477</v>
+        <v>47.34460067749023</v>
       </c>
       <c r="C109" t="n">
         <v>69.05999755859375</v>
@@ -3112,7 +3124,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
@@ -3141,11 +3153,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>45.18428039550781</v>
+        <v>45.18427658081055</v>
       </c>
       <c r="C111" t="n">
         <v>65.19999694824219</v>
@@ -3170,11 +3182,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>43.14682388305664</v>
+        <v>43.14683151245117</v>
       </c>
       <c r="C112" t="n">
         <v>62.2599983215332</v>
@@ -3199,11 +3211,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>47.06927108764648</v>
+        <v>47.06927871704102</v>
       </c>
       <c r="C113" t="n">
         <v>67.91999816894531</v>
@@ -3228,11 +3240,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>44.6312255859375</v>
+        <v>44.63121032714844</v>
       </c>
       <c r="C114" t="n">
         <v>63.68000030517578</v>
@@ -3257,11 +3269,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>43.04024887084961</v>
+        <v>43.04025650024414</v>
       </c>
       <c r="C115" t="n">
         <v>61.40999984741211</v>
@@ -3286,11 +3298,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>35.75558471679688</v>
+        <v>35.75557327270508</v>
       </c>
       <c r="C116" t="n">
         <v>50.34000015258789</v>
@@ -3315,11 +3327,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>34.91035461425781</v>
+        <v>34.91033554077148</v>
       </c>
       <c r="C117" t="n">
         <v>49.15000152587891</v>
@@ -3344,11 +3356,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>34.06511688232422</v>
+        <v>34.06510543823242</v>
       </c>
       <c r="C118" t="n">
         <v>47.95999908447266</v>
@@ -3373,11 +3385,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>38.40597915649414</v>
+        <v>38.40596771240234</v>
       </c>
       <c r="C119" t="n">
         <v>53.34999847412109</v>
@@ -3402,11 +3414,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>38.90988540649414</v>
+        <v>38.90990829467773</v>
       </c>
       <c r="C120" t="n">
         <v>54.04999923706055</v>
@@ -3429,11 +3441,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>33.61153030395508</v>
+        <v>33.61152648925781</v>
       </c>
       <c r="C121" t="n">
         <v>46.68999862670898</v>
@@ -3456,11 +3468,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>28.13318824768066</v>
+        <v>28.13318634033203</v>
       </c>
       <c r="C122" t="n">
         <v>39.08000183105469</v>
@@ -3483,11 +3495,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>24.54350280761719</v>
+        <v>24.54351806640625</v>
       </c>
       <c r="C123" t="n">
         <v>33.83000183105469</v>
@@ -3510,11 +3522,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>29.2157039642334</v>
+        <v>29.21570777893066</v>
       </c>
       <c r="C124" t="n">
         <v>40.27000045776367</v>
@@ -3537,11 +3549,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>34.67142486572266</v>
+        <v>34.67142868041992</v>
       </c>
       <c r="C125" t="n">
         <v>47.79000091552734</v>
@@ -3564,7 +3576,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
@@ -3591,11 +3603,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>31.81326866149902</v>
+        <v>31.81328010559082</v>
       </c>
       <c r="C127" t="n">
         <v>43.59999847412109</v>
@@ -3618,11 +3630,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>29.96303367614746</v>
+        <v>29.96303749084473</v>
       </c>
       <c r="C128" t="n">
         <v>40.81999969482422</v>
@@ -3645,11 +3657,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>30.13184356689453</v>
+        <v>30.13186264038086</v>
       </c>
       <c r="C129" t="n">
         <v>41.04999923706055</v>
@@ -3672,11 +3684,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>31.90820503234863</v>
+        <v>31.90821266174316</v>
       </c>
       <c r="C130" t="n">
         <v>43.47000122070312</v>
@@ -3699,7 +3711,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
@@ -3726,11 +3738,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>35.82106399536133</v>
+        <v>35.82105255126953</v>
       </c>
       <c r="C132" t="n">
         <v>48.52000045776367</v>
@@ -3753,11 +3765,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>37.01707077026367</v>
+        <v>37.01705932617188</v>
       </c>
       <c r="C133" t="n">
         <v>50.13999938964844</v>
@@ -3780,11 +3792,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>35.99824523925781</v>
+        <v>35.99823760986328</v>
       </c>
       <c r="C134" t="n">
         <v>48.7599983215332</v>
@@ -3807,11 +3819,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>35.30753707885742</v>
+        <v>35.30754089355469</v>
       </c>
       <c r="C135" t="n">
         <v>47.56999969482422</v>
@@ -3834,11 +3846,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>37.01464080810547</v>
+        <v>37.01465606689453</v>
       </c>
       <c r="C136" t="n">
         <v>49.86999893188477</v>
@@ -3861,7 +3873,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
@@ -3888,11 +3900,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>33.3556022644043</v>
+        <v>33.35560989379883</v>
       </c>
       <c r="C138" t="n">
         <v>44.68999862670898</v>
@@ -3915,11 +3927,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>32.81075668334961</v>
+        <v>32.81072998046875</v>
       </c>
       <c r="C139" t="n">
         <v>43.95999908447266</v>
@@ -3942,11 +3954,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>34.06992340087891</v>
+        <v>34.06991958618164</v>
       </c>
       <c r="C140" t="n">
         <v>45.36999893188477</v>
@@ -3969,11 +3981,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>32.78582000732422</v>
+        <v>32.78582382202148</v>
       </c>
       <c r="C141" t="n">
         <v>43.65999984741211</v>
@@ -3996,11 +4008,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>37.58430099487305</v>
+        <v>37.58430862426758</v>
       </c>
       <c r="C142" t="n">
         <v>50.04999923706055</v>
@@ -4023,11 +4035,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>38.61578369140625</v>
+        <v>38.61577606201172</v>
       </c>
       <c r="C143" t="n">
         <v>51.15000152587891</v>
@@ -4050,7 +4062,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
@@ -4077,7 +4089,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -4104,11 +4116,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>44.39870452880859</v>
+        <v>44.39870071411133</v>
       </c>
       <c r="C146" t="n">
         <v>58.81000137329102</v>
@@ -4131,11 +4143,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>41.22208404541016</v>
+        <v>41.22208786010742</v>
       </c>
       <c r="C147" t="n">
         <v>54.31000137329102</v>
@@ -4158,11 +4170,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>45.00199127197266</v>
+        <v>45.00196838378906</v>
       </c>
       <c r="C148" t="n">
         <v>59.29000091552734</v>
@@ -4185,11 +4197,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>49.71546173095703</v>
+        <v>49.71545028686523</v>
       </c>
       <c r="C149" t="n">
         <v>65.5</v>
@@ -4212,11 +4224,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>51.36110305786133</v>
+        <v>51.36109924316406</v>
       </c>
       <c r="C150" t="n">
         <v>67.38999938964844</v>
@@ -4239,11 +4251,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>53.0606803894043</v>
+        <v>53.06067276000977</v>
       </c>
       <c r="C151" t="n">
         <v>69.62000274658203</v>
@@ -4266,11 +4278,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>55.23002243041992</v>
+        <v>55.23001098632812</v>
       </c>
       <c r="C152" t="n">
         <v>72.16999816894531</v>
@@ -4293,11 +4305,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>56.19426345825195</v>
+        <v>56.19426727294922</v>
       </c>
       <c r="C153" t="n">
         <v>73.43000030517578</v>
@@ -4322,7 +4334,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
@@ -4351,11 +4363,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>53.71793746948242</v>
+        <v>53.71792221069336</v>
       </c>
       <c r="C155" t="n">
         <v>69.90000152587891</v>
@@ -4380,11 +4392,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>50.859130859375</v>
+        <v>50.85912322998047</v>
       </c>
       <c r="C156" t="n">
         <v>66.18000030517578</v>
@@ -4409,11 +4421,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>47.91577529907227</v>
+        <v>47.91577911376953</v>
       </c>
       <c r="C157" t="n">
         <v>62.34999847412109</v>
@@ -4438,11 +4450,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>52.01955795288086</v>
+        <v>52.01955413818359</v>
       </c>
       <c r="C158" t="n">
         <v>67.69000244140625</v>
@@ -4467,11 +4479,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>52.37925338745117</v>
+        <v>52.37925720214844</v>
       </c>
       <c r="C159" t="n">
         <v>67.84999847412109</v>
@@ -4496,11 +4508,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>51.5223503112793</v>
+        <v>51.52235794067383</v>
       </c>
       <c r="C160" t="n">
         <v>66.73999786376953</v>
@@ -4525,11 +4537,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>48.7277717590332</v>
+        <v>48.72776031494141</v>
       </c>
       <c r="C161" t="n">
         <v>63.11999893188477</v>
@@ -4554,11 +4566,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>45.74300765991211</v>
+        <v>45.74301528930664</v>
       </c>
       <c r="C162" t="n">
         <v>58.95999908447266</v>
@@ -4583,11 +4595,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>47.32571411132812</v>
+        <v>47.32571029663086</v>
       </c>
       <c r="C163" t="n">
         <v>61</v>
@@ -4612,11 +4624,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>46.06905746459961</v>
+        <v>46.06905364990234</v>
       </c>
       <c r="C164" t="n">
         <v>59.08000183105469</v>
@@ -4641,11 +4653,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>40.68861770629883</v>
+        <v>40.68862152099609</v>
       </c>
       <c r="C165" t="n">
         <v>52.18000030517578</v>
@@ -4670,11 +4682,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>44.43153762817383</v>
+        <v>44.4315299987793</v>
       </c>
       <c r="C166" t="n">
         <v>56.97999954223633</v>
@@ -4699,11 +4711,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>43.36909103393555</v>
+        <v>43.36909484863281</v>
       </c>
       <c r="C167" t="n">
         <v>55.20000076293945</v>
@@ -4728,11 +4740,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>47.09317398071289</v>
+        <v>47.09318161010742</v>
       </c>
       <c r="C168" t="n">
         <v>59.93999862670898</v>
@@ -4757,11 +4769,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>51.09225463867188</v>
+        <v>51.09225082397461</v>
       </c>
       <c r="C169" t="n">
         <v>65.02999877929688</v>
@@ -4786,11 +4798,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>46.69248199462891</v>
+        <v>46.69248580932617</v>
       </c>
       <c r="C170" t="n">
         <v>59.43000030517578</v>
@@ -4815,11 +4827,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>38.31149673461914</v>
+        <v>38.31148910522461</v>
       </c>
       <c r="C171" t="n">
         <v>48.41999816894531</v>
@@ -4844,11 +4856,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>24.36997413635254</v>
+        <v>24.36997032165527</v>
       </c>
       <c r="C172" t="n">
         <v>30.79999923706055</v>
@@ -4873,11 +4885,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>33.31090545654297</v>
+        <v>33.31089782714844</v>
       </c>
       <c r="C173" t="n">
         <v>42.09999847412109</v>
@@ -4902,11 +4914,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>33.70794296264648</v>
+        <v>33.70795059204102</v>
       </c>
       <c r="C174" t="n">
         <v>42.18000030517578</v>
@@ -4931,7 +4943,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -4956,11 +4968,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>30.18486976623535</v>
+        <v>30.18486404418945</v>
       </c>
       <c r="C176" t="n">
         <v>37.38999938964844</v>
@@ -4981,11 +4993,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>30.5885181427002</v>
+        <v>30.58851051330566</v>
       </c>
       <c r="C177" t="n">
         <v>37.88999938964844</v>
@@ -5006,11 +5018,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>26.51165390014648</v>
+        <v>26.51165771484375</v>
       </c>
       <c r="C178" t="n">
         <v>32.84000015258789</v>
@@ -5031,11 +5043,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>23.38896751403809</v>
+        <v>23.38896560668945</v>
       </c>
       <c r="C179" t="n">
         <v>28.6200008392334</v>
@@ -5056,7 +5068,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -5081,11 +5093,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>32.68080902099609</v>
+        <v>32.68081283569336</v>
       </c>
       <c r="C181" t="n">
         <v>39.9900016784668</v>
@@ -5106,11 +5118,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>32.71349334716797</v>
+        <v>32.7134895324707</v>
       </c>
       <c r="C182" t="n">
         <v>40.02999877929688</v>
@@ -5131,11 +5143,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>42.89420318603516</v>
+        <v>42.89419937133789</v>
       </c>
       <c r="C183" t="n">
         <v>52.0099983215332</v>
@@ -5156,11 +5168,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>43.68593978881836</v>
+        <v>43.68595123291016</v>
       </c>
       <c r="C184" t="n">
         <v>52.97000122070312</v>
@@ -5181,11 +5193,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>42.17668533325195</v>
+        <v>42.17669677734375</v>
       </c>
       <c r="C185" t="n">
         <v>51.13999938964844</v>
@@ -5206,7 +5218,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
@@ -5231,11 +5243,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>50.61687850952148</v>
+        <v>50.61688613891602</v>
       </c>
       <c r="C187" t="n">
         <v>60.90000152587891</v>
@@ -5256,11 +5268,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>46.95038604736328</v>
+        <v>46.95037460327148</v>
       </c>
       <c r="C188" t="n">
         <v>56.06000137329102</v>
@@ -5281,11 +5293,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>46.50650024414062</v>
+        <v>46.50650787353516</v>
       </c>
       <c r="C189" t="n">
         <v>55.52999877929688</v>
@@ -5306,11 +5318,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>56.75753784179688</v>
+        <v>56.75753021240234</v>
       </c>
       <c r="C190" t="n">
         <v>67.76999664306641</v>
@@ -5331,11 +5343,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>62.76033020019531</v>
+        <v>62.76032638549805</v>
       </c>
       <c r="C191" t="n">
         <v>74.48999786376953</v>
@@ -5356,11 +5368,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>59.08687973022461</v>
+        <v>59.08689117431641</v>
       </c>
       <c r="C192" t="n">
         <v>70.12999725341797</v>
@@ -5381,11 +5393,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>60.98281478881836</v>
+        <v>60.98282241821289</v>
       </c>
       <c r="C193" t="n">
         <v>72.18000030517578</v>
@@ -5406,11 +5418,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>74.87251281738281</v>
+        <v>74.87249755859375</v>
       </c>
       <c r="C194" t="n">
         <v>88.62000274658203</v>
@@ -5431,11 +5443,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>80.54763793945312</v>
+        <v>80.54763031005859</v>
       </c>
       <c r="C195" t="n">
         <v>94.86000061035156</v>
@@ -5460,11 +5472,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>85.16586303710938</v>
+        <v>85.16584777832031</v>
       </c>
       <c r="C196" t="n">
         <v>100</v>
@@ -5489,7 +5501,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5518,11 +5530,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>96.12202453613281</v>
+        <v>96.12200927734375</v>
       </c>
       <c r="C198" t="n">
         <v>112.3600006103516</v>
@@ -5547,7 +5559,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -5576,7 +5588,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -5605,11 +5617,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>94.78347015380859</v>
+        <v>94.78346252441406</v>
       </c>
       <c r="C201" t="n">
         <v>109.4499969482422</v>
@@ -5634,11 +5646,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>89.90061950683594</v>
+        <v>89.90061187744141</v>
       </c>
       <c r="C202" t="n">
         <v>102.3399963378906</v>
@@ -5663,7 +5675,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -5692,7 +5704,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
@@ -5721,11 +5733,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>104.7024688720703</v>
+        <v>104.7024993896484</v>
       </c>
       <c r="C205" t="n">
         <v>118</v>
@@ -5750,11 +5762,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>108.1363677978516</v>
+        <v>108.1363906860352</v>
       </c>
       <c r="C206" t="n">
         <v>121.870002746582</v>
@@ -5779,11 +5791,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>92.11167907714844</v>
+        <v>92.11167144775391</v>
       </c>
       <c r="C207" t="n">
         <v>103.3499984741211</v>
@@ -5808,7 +5820,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5837,11 +5849,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>92.26964569091797</v>
+        <v>92.26963043212891</v>
       </c>
       <c r="C209" t="n">
         <v>102.8899993896484</v>
@@ -5866,7 +5878,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -5895,7 +5907,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -5924,11 +5936,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>106.7507400512695</v>
+        <v>106.7507247924805</v>
       </c>
       <c r="C212" t="n">
         <v>117.7200012207031</v>
@@ -5953,11 +5965,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>108.4084396362305</v>
+        <v>108.4084548950195</v>
       </c>
       <c r="C213" t="n">
         <v>119.0299987792969</v>
@@ -5982,7 +5994,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6011,7 +6023,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6040,7 +6052,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
@@ -6069,7 +6081,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6098,11 +6110,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>102.9150695800781</v>
+        <v>102.9150619506836</v>
       </c>
       <c r="C218" t="n">
         <v>111.870002746582</v>
@@ -6127,11 +6139,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>104.2700119018555</v>
+        <v>104.2699890136719</v>
       </c>
       <c r="C219" t="n">
         <v>112.5400009155273</v>
@@ -6156,11 +6168,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>117.9268341064453</v>
+        <v>117.9268264770508</v>
       </c>
       <c r="C220" t="n">
         <v>127.2799987792969</v>
@@ -6185,11 +6197,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>116.3888092041016</v>
+        <v>116.388801574707</v>
       </c>
       <c r="C221" t="n">
         <v>125.620002746582</v>
@@ -6214,11 +6226,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>108.6070098876953</v>
+        <v>108.6070175170898</v>
       </c>
       <c r="C222" t="n">
         <v>116.4800033569336</v>
@@ -6243,11 +6255,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>106.6489639282227</v>
+        <v>106.6489486694336</v>
       </c>
       <c r="C223" t="n">
         <v>114.379997253418</v>
@@ -6272,11 +6284,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>103.6838836669922</v>
+        <v>103.6838912963867</v>
       </c>
       <c r="C224" t="n">
         <v>111.1999969482422</v>
@@ -6301,7 +6313,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6330,7 +6342,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6359,11 +6371,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>102.8749084472656</v>
+        <v>102.8749160766602</v>
       </c>
       <c r="C227" t="n">
         <v>109.5400009155273</v>
@@ -6388,11 +6400,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>102.4589309692383</v>
+        <v>102.4589385986328</v>
       </c>
       <c r="C228" t="n">
         <v>108.3399963378906</v>
@@ -6417,7 +6429,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6446,11 +6458,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>93.46517181396484</v>
+        <v>93.46517944335938</v>
       </c>
       <c r="C230" t="n">
         <v>98.83000183105469</v>
@@ -6475,7 +6487,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6504,7 +6516,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6533,11 +6545,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>84.96620941162109</v>
+        <v>84.96620178222656</v>
       </c>
       <c r="C233" t="n">
         <v>89.12000274658203</v>
@@ -6562,7 +6574,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6591,11 +6603,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>86.28544616699219</v>
+        <v>86.28545379638672</v>
       </c>
       <c r="C235" t="n">
         <v>89.73999786376953</v>
@@ -6620,7 +6632,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6649,7 +6661,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6678,7 +6690,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6707,11 +6719,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>86.14418029785156</v>
+        <v>86.14417266845703</v>
       </c>
       <c r="C239" t="n">
         <v>88.86000061035156</v>
@@ -6736,7 +6748,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6765,7 +6777,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6794,11 +6806,11 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>101.9819869995117</v>
+        <v>101.9819793701172</v>
       </c>
       <c r="C242" t="n">
         <v>104.2300033569336</v>
@@ -6823,7 +6835,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6852,7 +6864,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6881,11 +6893,11 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>124.0249099731445</v>
+        <v>124.0249176025391</v>
       </c>
       <c r="C245" t="n">
         <v>125.7799987792969</v>
@@ -6910,7 +6922,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -6939,7 +6951,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -6968,7 +6980,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -6997,7 +7009,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7026,32 +7038,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>128.0899963378906</v>
+        <v>129.3399963378906</v>
       </c>
       <c r="C250" t="n">
-        <v>128.0899963378906</v>
+        <v>129.3399963378906</v>
       </c>
       <c r="D250" t="n">
-        <v>113071500</v>
+        <v>118433100</v>
       </c>
       <c r="E250" t="n">
         <v>7.57</v>
       </c>
       <c r="F250" t="n">
-        <v>16.92073927845319</v>
+        <v>17.08586477382967</v>
       </c>
       <c r="G250" t="n">
         <v>1201337479</v>
       </c>
       <c r="H250" t="n">
-        <v>153879313285.6808</v>
+        <v>155380985134.4308</v>
       </c>
       <c r="I250" t="n">
-        <v>0.09412134556404696</v>
+        <v>0.09858437122812848</v>
       </c>
     </row>
   </sheetData>
@@ -7083,75 +7095,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40029</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7187,13 +7199,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40120</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7229,13 +7241,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40302</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7271,13 +7283,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40029</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7313,13 +7325,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40120</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7355,13 +7367,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40302</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7397,13 +7409,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40395</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7439,13 +7451,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40484</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7481,13 +7493,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7514,7 +7526,7 @@
       <c r="I10" t="n">
         <v>5.80885217233538</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="K10" t="n">
@@ -7527,13 +7539,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40666</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7560,7 +7572,7 @@
       <c r="I11" t="n">
         <v>6.334850597389371</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40666</v>
       </c>
       <c r="K11" t="n">
@@ -7573,13 +7585,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40757</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7606,7 +7618,7 @@
       <c r="I12" t="n">
         <v>6.060416636491636</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40757</v>
       </c>
       <c r="K12" t="n">
@@ -7619,13 +7631,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7652,7 +7664,7 @@
       <c r="I13" t="n">
         <v>5.95369231836474</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="K13" t="n">
@@ -7665,13 +7677,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40960</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7698,7 +7710,7 @@
       <c r="I14" t="n">
         <v>6.837979525701884</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40960</v>
       </c>
       <c r="K14" t="n">
@@ -7711,13 +7723,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7744,7 +7756,7 @@
       <c r="I15" t="n">
         <v>6.975196506150751</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="K15" t="n">
@@ -7757,13 +7769,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7790,7 +7802,7 @@
       <c r="I16" t="n">
         <v>6.938013601252029</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="K16" t="n">
@@ -7803,13 +7815,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41212</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7836,7 +7848,7 @@
       <c r="I17" t="n">
         <v>6.941988975377937</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41212</v>
       </c>
       <c r="K17" t="n">
@@ -7849,13 +7861,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41324</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7882,7 +7894,7 @@
       <c r="I18" t="n">
         <v>6.719999999999999</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41324</v>
       </c>
       <c r="K18" t="n">
@@ -7895,13 +7907,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -7928,7 +7940,7 @@
       <c r="I19" t="n">
         <v>6.719541413228174</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="K19" t="n">
@@ -7941,13 +7953,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41488</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -7974,7 +7986,7 @@
       <c r="I20" t="n">
         <v>6.569541413228174</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41488</v>
       </c>
       <c r="K20" t="n">
@@ -7987,13 +7999,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41583</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8020,7 +8032,7 @@
       <c r="I21" t="n">
         <v>7.109541413228174</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41583</v>
       </c>
       <c r="K21" t="n">
@@ -8033,13 +8045,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41695</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8066,7 +8078,7 @@
       <c r="I22" t="n">
         <v>7.380000000000001</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41695</v>
       </c>
       <c r="K22" t="n">
@@ -8079,13 +8091,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41765</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8112,7 +8124,7 @@
       <c r="I23" t="n">
         <v>7.359999999999999</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41765</v>
       </c>
       <c r="K23" t="n">
@@ -8125,13 +8137,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41856</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8158,7 +8170,7 @@
       <c r="I24" t="n">
         <v>7.379999999999999</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41856</v>
       </c>
       <c r="K24" t="n">
@@ -8171,13 +8183,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41947</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8204,7 +8216,7 @@
       <c r="I25" t="n">
         <v>7.549999999999999</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41947</v>
       </c>
       <c r="K25" t="n">
@@ -8217,13 +8229,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42059</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8250,7 +8262,7 @@
       <c r="I26" t="n">
         <v>5.51</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42059</v>
       </c>
       <c r="K26" t="n">
@@ -8263,13 +8275,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42129</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8296,7 +8308,7 @@
       <c r="I27" t="n">
         <v>4.02</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42129</v>
       </c>
       <c r="K27" t="n">
@@ -8309,13 +8321,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42220</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8342,7 +8354,7 @@
       <c r="I28" t="n">
         <v>2.2</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42220</v>
       </c>
       <c r="K28" t="n">
@@ -8355,13 +8367,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42311</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8388,7 +8400,7 @@
       <c r="I29" t="n">
         <v>-0.8400000000000001</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42311</v>
       </c>
       <c r="K29" t="n">
@@ -8401,13 +8413,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42423</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8434,7 +8446,7 @@
       <c r="I30" t="n">
         <v>-3.58</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42423</v>
       </c>
       <c r="K30" t="n">
@@ -8447,13 +8459,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42493</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8480,7 +8492,7 @@
       <c r="I31" t="n">
         <v>-4.98</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42493</v>
       </c>
       <c r="K31" t="n">
@@ -8493,13 +8505,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42584</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8526,7 +8538,7 @@
       <c r="I32" t="n">
         <v>-5.69</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42584</v>
       </c>
       <c r="K32" t="n">
@@ -8539,13 +8551,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8572,7 +8584,7 @@
       <c r="I33" t="n">
         <v>-5.66</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="K33" t="n">
@@ -8585,13 +8597,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42787</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8618,7 +8630,7 @@
       <c r="I34" t="n">
         <v>-2.91</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42787</v>
       </c>
       <c r="K34" t="n">
@@ -8631,13 +8643,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8664,7 +8676,7 @@
       <c r="I35" t="n">
         <v>-1.26</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="K35" t="n">
@@ -8677,13 +8689,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8710,7 +8722,7 @@
       <c r="I36" t="n">
         <v>-3.18</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="K36" t="n">
@@ -8723,13 +8735,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8756,7 +8768,7 @@
       <c r="I37" t="n">
         <v>-2</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="K37" t="n">
@@ -8769,13 +8781,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43151</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8802,7 +8814,7 @@
       <c r="I38" t="n">
         <v>-0.6999999999999997</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43151</v>
       </c>
       <c r="K38" t="n">
@@ -8815,13 +8827,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8848,7 +8860,7 @@
       <c r="I39" t="n">
         <v>-0.4199999999999999</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="K39" t="n">
@@ -8861,13 +8873,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8894,7 +8906,7 @@
       <c r="I40" t="n">
         <v>3.75</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43313</v>
       </c>
       <c r="K40" t="n">
@@ -8907,13 +8919,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -8940,7 +8952,7 @@
       <c r="I41" t="n">
         <v>5</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="K41" t="n">
@@ -8953,13 +8965,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43515</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -8986,7 +8998,7 @@
       <c r="I42" t="n">
         <v>5.340000000000001</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43515</v>
       </c>
       <c r="K42" t="n">
@@ -8999,13 +9011,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43587</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9032,7 +9044,7 @@
       <c r="I43" t="n">
         <v>6.190000000000001</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43587</v>
       </c>
       <c r="K43" t="n">
@@ -9045,13 +9057,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9078,7 +9090,7 @@
       <c r="I44" t="n">
         <v>6.2</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="K44" t="n">
@@ -9091,13 +9103,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9124,7 +9136,7 @@
       <c r="I45" t="n">
         <v>7.350000000000001</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="K45" t="n">
@@ -9137,13 +9149,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>44609</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9170,7 +9182,7 @@
       <c r="I46" t="n">
         <v>6.4</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>44609</v>
       </c>
       <c r="K46" t="n">
@@ -9183,13 +9195,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43956</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9216,7 +9228,7 @@
       <c r="I47" t="n">
         <v>3.200000000000001</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>44609</v>
       </c>
       <c r="K47" t="n">
@@ -9229,13 +9241,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44047</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9262,7 +9274,7 @@
       <c r="I48" t="n">
         <v>2.04</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44609</v>
       </c>
       <c r="K48" t="n">
@@ -9275,13 +9287,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44138</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9308,7 +9320,7 @@
       <c r="I49" t="n">
         <v>-1.12</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44609</v>
       </c>
       <c r="K49" t="n">
@@ -9321,13 +9333,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44609</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9354,7 +9366,7 @@
       <c r="I50" t="n">
         <v>-2.51</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44609</v>
       </c>
       <c r="K50" t="n">
@@ -9367,13 +9379,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9400,7 +9412,7 @@
       <c r="I51" t="n">
         <v>-0.1599999999999995</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44609</v>
       </c>
       <c r="K51" t="n">
@@ -9413,13 +9425,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9446,7 +9458,7 @@
       <c r="I52" t="n">
         <v>1.150000000000001</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44609</v>
       </c>
       <c r="K52" t="n">
@@ -9459,13 +9471,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9492,7 +9504,7 @@
       <c r="I53" t="n">
         <v>3.350000000000001</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44609</v>
       </c>
       <c r="K53" t="n">
@@ -9505,13 +9517,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44609</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9538,7 +9550,7 @@
       <c r="I54" t="n">
         <v>6.07</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44609</v>
       </c>
       <c r="K54" t="n">
@@ -9551,13 +9563,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9584,7 +9596,7 @@
       <c r="I55" t="n">
         <v>9.710000000000001</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="K55" t="n">
@@ -9597,13 +9609,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9630,7 +9642,7 @@
       <c r="I56" t="n">
         <v>12.12</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="K56" t="n">
@@ -9643,13 +9655,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9676,7 +9688,7 @@
       <c r="I57" t="n">
         <v>13.89</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="K57" t="n">
@@ -9689,13 +9701,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44973</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9722,7 +9734,7 @@
       <c r="I58" t="n">
         <v>14.57</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44973</v>
       </c>
       <c r="K58" t="n">
@@ -9735,13 +9747,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9768,7 +9780,7 @@
       <c r="I59" t="n">
         <v>12.56</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="K59" t="n">
@@ -9781,13 +9793,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9814,7 +9826,7 @@
       <c r="I60" t="n">
         <v>10.44</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="K60" t="n">
@@ -9827,13 +9839,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9860,7 +9872,7 @@
       <c r="I61" t="n">
         <v>9.210000000000001</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="K61" t="n">
@@ -9873,13 +9885,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45337</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9906,7 +9918,7 @@
       <c r="I62" t="n">
         <v>9.060000000000002</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45337</v>
       </c>
       <c r="K62" t="n">
@@ -9919,13 +9931,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -9952,7 +9964,7 @@
       <c r="I63" t="n">
         <v>8.830000000000002</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="K63" t="n">
@@ -9965,13 +9977,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -9998,7 +10010,7 @@
       <c r="I64" t="n">
         <v>8.970000000000002</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="K64" t="n">
@@ -10011,13 +10023,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10044,7 +10056,7 @@
       <c r="I65" t="n">
         <v>8.410000000000002</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="K65" t="n">
@@ -10057,13 +10069,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45706</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10090,7 +10102,7 @@
       <c r="I66" t="n">
         <v>7.81</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45706</v>
       </c>
       <c r="K66" t="n">
@@ -10103,13 +10115,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45785</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10136,7 +10148,7 @@
       <c r="I67" t="n">
         <v>7.890000000000001</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45785</v>
       </c>
       <c r="K67" t="n">
@@ -10149,13 +10161,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10182,7 +10194,7 @@
       <c r="I68" t="n">
         <v>7.470000000000001</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="K68" t="n">
@@ -10195,13 +10207,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10228,7 +10240,7 @@
       <c r="I69" t="n">
         <v>7.09</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="K69" t="n">
@@ -10241,13 +10253,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46070</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10274,7 +10286,7 @@
       <c r="I70" t="n">
         <v>6.35</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46070</v>
       </c>
       <c r="K70" t="n">
@@ -10287,13 +10299,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10320,7 +10332,7 @@
       <c r="I71" t="n">
         <v>5.899999999999999</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="K71" t="n">
@@ -10333,13 +10345,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10366,7 +10378,7 @@
       <c r="I72" t="n">
         <v>7.57</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="K72" t="n">
@@ -10403,52 +10415,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40029</v>
       </c>
       <c r="C2" t="n">
@@ -10477,10 +10489,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40120</v>
       </c>
       <c r="C3" t="n">
@@ -10509,10 +10521,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40234</v>
       </c>
       <c r="C4" t="n">
@@ -10541,10 +10553,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40302</v>
       </c>
       <c r="C5" t="n">
@@ -10573,10 +10585,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40395</v>
       </c>
       <c r="C6" t="n">
@@ -10605,10 +10617,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40484</v>
       </c>
       <c r="C7" t="n">
@@ -10637,10 +10649,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="C8" t="n">
@@ -10669,10 +10681,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40666</v>
       </c>
       <c r="C9" t="n">
@@ -10701,10 +10713,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40757</v>
       </c>
       <c r="C10" t="n">
@@ -10733,10 +10745,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="C11" t="n">
@@ -10765,10 +10777,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40960</v>
       </c>
       <c r="C12" t="n">
@@ -10797,10 +10809,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="C13" t="n">
@@ -10829,10 +10841,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="C14" t="n">
@@ -10861,10 +10873,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41212</v>
       </c>
       <c r="C15" t="n">
@@ -10893,10 +10905,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41324</v>
       </c>
       <c r="C16" t="n">
@@ -10925,10 +10937,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="C17" t="n">
@@ -10957,10 +10969,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41488</v>
       </c>
       <c r="C18" t="n">
@@ -10989,10 +11001,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41583</v>
       </c>
       <c r="C19" t="n">
@@ -11021,10 +11033,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41695</v>
       </c>
       <c r="C20" t="n">
@@ -11053,10 +11065,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41765</v>
       </c>
       <c r="C21" t="n">
@@ -11085,10 +11097,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41856</v>
       </c>
       <c r="C22" t="n">
@@ -11117,10 +11129,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41947</v>
       </c>
       <c r="C23" t="n">
@@ -11149,10 +11161,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42059</v>
       </c>
       <c r="C24" t="n">
@@ -11181,10 +11193,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42129</v>
       </c>
       <c r="C25" t="n">
@@ -11213,10 +11225,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42220</v>
       </c>
       <c r="C26" t="n">
@@ -11245,10 +11257,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42311</v>
       </c>
       <c r="C27" t="n">
@@ -11277,10 +11289,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42423</v>
       </c>
       <c r="C28" t="n">
@@ -11309,10 +11321,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42493</v>
       </c>
       <c r="C29" t="n">
@@ -11341,10 +11353,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42584</v>
       </c>
       <c r="C30" t="n">
@@ -11373,10 +11385,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="C31" t="n">
@@ -11405,10 +11417,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42787</v>
       </c>
       <c r="C32" t="n">
@@ -11437,10 +11449,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="C33" t="n">
@@ -11469,10 +11481,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42948</v>
       </c>
       <c r="C34" t="n">
@@ -11501,10 +11513,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="C35" t="n">
@@ -11533,10 +11545,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43151</v>
       </c>
       <c r="C36" t="n">
@@ -11565,10 +11577,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="C37" t="n">
@@ -11597,10 +11609,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="C38" t="n">
@@ -11629,10 +11641,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="C39" t="n">
@@ -11661,10 +11673,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43515</v>
       </c>
       <c r="C40" t="n">
@@ -11693,10 +11705,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43587</v>
       </c>
       <c r="C41" t="n">
@@ -11725,10 +11737,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="C42" t="n">
@@ -11757,10 +11769,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="C43" t="n">
@@ -11789,10 +11801,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43879</v>
       </c>
       <c r="C44" t="n">
@@ -11821,10 +11833,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43956</v>
       </c>
       <c r="C45" t="n">
@@ -11853,10 +11865,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44047</v>
       </c>
       <c r="C46" t="n">
@@ -11885,10 +11897,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44138</v>
       </c>
       <c r="C47" t="n">
@@ -11917,10 +11929,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44243</v>
       </c>
       <c r="C48" t="n">
@@ -11949,10 +11961,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="C49" t="n">
@@ -11981,10 +11993,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="C50" t="n">
@@ -12013,10 +12025,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="C51" t="n">
@@ -12045,10 +12057,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44609</v>
       </c>
       <c r="C52" t="n">
@@ -12077,10 +12089,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="C53" t="n">
@@ -12109,10 +12121,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="C54" t="n">
@@ -12141,10 +12153,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="C55" t="n">
@@ -12173,10 +12185,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44973</v>
       </c>
       <c r="C56" t="n">
@@ -12205,10 +12217,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="C57" t="n">
@@ -12237,10 +12249,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="C58" t="n">
@@ -12269,10 +12281,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="C59" t="n">
@@ -12301,10 +12313,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45337</v>
       </c>
       <c r="C60" t="n">
@@ -12333,10 +12345,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="C61" t="n">
@@ -12365,10 +12377,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="C62" t="n">
@@ -12397,10 +12409,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="C63" t="n">
@@ -12429,10 +12441,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45706</v>
       </c>
       <c r="C64" t="n">
@@ -12461,10 +12473,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45785</v>
       </c>
       <c r="C65" t="n">
@@ -12493,10 +12505,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="C66" t="n">
@@ -12525,10 +12537,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="C67" t="n">
@@ -12557,10 +12569,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46070</v>
       </c>
       <c r="C68" t="n">
@@ -12589,10 +12601,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="C69" t="n">
@@ -12621,10 +12633,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="C70" t="n">
@@ -12671,12 +12683,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/COP.xlsx
+++ b/salidas/empresas/COP.xlsx
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>23.43121147155762</v>
+        <v>23.43121528625488</v>
       </c>
       <c r="C3" t="n">
         <v>46.47081756591797</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>24.27297782897949</v>
+        <v>24.27297973632812</v>
       </c>
       <c r="C4" t="n">
         <v>48.14028930664062</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>25.7143611907959</v>
+        <v>25.71437454223633</v>
       </c>
       <c r="C5" t="n">
         <v>50.99897766113281</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>24.4654712677002</v>
+        <v>24.46547317504883</v>
       </c>
       <c r="C6" t="n">
         <v>48.24701690673828</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>25.33137512207031</v>
+        <v>25.33136177062988</v>
       </c>
       <c r="C7" t="n">
         <v>49.95460510253906</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>26.67356872558594</v>
+        <v>26.67355728149414</v>
       </c>
       <c r="C8" t="n">
         <v>52.32540893554688</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>24.64893531799316</v>
+        <v>24.64895439147949</v>
       </c>
       <c r="C9" t="n">
         <v>48.35374069213867</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>23.54559135437012</v>
+        <v>23.54558181762695</v>
       </c>
       <c r="C11" t="n">
         <v>45.92194747924805</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>26.30507278442383</v>
+        <v>26.3050708770752</v>
       </c>
       <c r="C12" t="n">
         <v>51.30390548706055</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>28.12259674072266</v>
+        <v>28.12258720397949</v>
       </c>
       <c r="C13" t="n">
         <v>54.84867477416992</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>25.95720481872559</v>
+        <v>25.95719909667969</v>
       </c>
       <c r="C14" t="n">
         <v>50.62544250488281</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>25.68728828430176</v>
+        <v>25.68728446960449</v>
       </c>
       <c r="C15" t="n">
         <v>49.79451751708984</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>26.87883949279785</v>
+        <v>26.87884330749512</v>
       </c>
       <c r="C16" t="n">
         <v>52.10433578491211</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>27.27209663391113</v>
+        <v>27.27208518981934</v>
       </c>
       <c r="C17" t="n">
         <v>52.86665344238281</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>30.62434005737305</v>
+        <v>30.62433052062988</v>
       </c>
       <c r="C18" t="n">
         <v>59.02617263793945</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>32.13406372070312</v>
+        <v>32.13406753540039</v>
       </c>
       <c r="C20" t="n">
         <v>61.62567138671875</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>33.93584060668945</v>
+        <v>33.93582916259766</v>
       </c>
       <c r="C23" t="n">
         <v>64.76641845703125</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>31.97061538696289</v>
+        <v>31.97061920166016</v>
       </c>
       <c r="C24" t="n">
         <v>61.01581573486328</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>35.26993942260742</v>
+        <v>35.26993560791016</v>
       </c>
       <c r="C25" t="n">
         <v>67.31255340576172</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>31.99858474731445</v>
+        <v>31.99857902526855</v>
       </c>
       <c r="C26" t="n">
         <v>61.06917953491211</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>33.2285041809082</v>
+        <v>33.22850799560547</v>
       </c>
       <c r="C27" t="n">
         <v>63.05120468139648</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>30.61714363098145</v>
+        <v>30.61713790893555</v>
       </c>
       <c r="C28" t="n">
         <v>58.09614562988281</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>34.61050033569336</v>
+        <v>34.61050796508789</v>
       </c>
       <c r="C29" t="n">
         <v>65.67356872558594</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>37.59299087524414</v>
+        <v>37.59297561645508</v>
       </c>
       <c r="C30" t="n">
         <v>70.97167205810547</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>33.14685821533203</v>
+        <v>33.14687347412109</v>
       </c>
       <c r="C32" t="n">
         <v>62.22027587890625</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>33.50830078125</v>
+        <v>33.50831604003906</v>
       </c>
       <c r="C33" t="n">
         <v>62.89873886108398</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>29.74771499633789</v>
+        <v>29.74771118164062</v>
       </c>
       <c r="C34" t="n">
         <v>55.83968734741211</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>21.32167053222656</v>
+        <v>21.3216724395752</v>
       </c>
       <c r="C35" t="n">
         <v>39.6480827331543</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>21.53074645996094</v>
+        <v>21.5307502746582</v>
       </c>
       <c r="C36" t="n">
         <v>40.036865234375</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>21.2355842590332</v>
+        <v>21.23558616638184</v>
       </c>
       <c r="C37" t="n">
         <v>39.48799896240234</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>19.48508071899414</v>
+        <v>19.48508262634277</v>
       </c>
       <c r="C38" t="n">
         <v>36.23290634155273</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>15.48392677307129</v>
+        <v>15.48391819000244</v>
       </c>
       <c r="C39" t="n">
         <v>28.4725227355957</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>16.23428344726562</v>
+        <v>16.23427963256836</v>
       </c>
       <c r="C40" t="n">
         <v>29.85231590270996</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>18.50048446655273</v>
+        <v>18.5004825592041</v>
       </c>
       <c r="C44" t="n">
         <v>33.32085800170898</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>19.11420631408691</v>
+        <v>19.11421012878418</v>
       </c>
       <c r="C46" t="n">
         <v>34.42621612548828</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>21.44757270812988</v>
+        <v>21.44757080078125</v>
       </c>
       <c r="C47" t="n">
         <v>38.25304412841797</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>22.12716484069824</v>
+        <v>22.12715721130371</v>
       </c>
       <c r="C48" t="n">
         <v>39.46512985229492</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>21.82796669006348</v>
+        <v>21.82797431945801</v>
       </c>
       <c r="C49" t="n">
         <v>38.9315071105957</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>20.72602653503418</v>
+        <v>20.72601890563965</v>
       </c>
       <c r="C51" t="n">
         <v>36.59119415283203</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>22.09480285644531</v>
+        <v>22.09480094909668</v>
       </c>
       <c r="C52" t="n">
         <v>39.00773620605469</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>25.55777168273926</v>
+        <v>25.55777359008789</v>
       </c>
       <c r="C53" t="n">
         <v>45.12151718139648</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>21.41514587402344</v>
+        <v>21.4151554107666</v>
       </c>
       <c r="C55" t="n">
         <v>37.422119140625</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>24.33518409729004</v>
+        <v>24.33516693115234</v>
       </c>
       <c r="C56" t="n">
         <v>42.09511947631836</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>23.10563087463379</v>
+        <v>23.10562705993652</v>
       </c>
       <c r="C57" t="n">
         <v>39.96825790405273</v>
@@ -1640,7 +1640,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>25.30911445617676</v>
+        <v>25.30911827087402</v>
       </c>
       <c r="C58" t="n">
         <v>43.77983856201172</v>
@@ -1665,7 +1665,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>26.40954780578613</v>
+        <v>26.40954399108887</v>
       </c>
       <c r="C59" t="n">
         <v>45.27397918701172</v>
@@ -1715,7 +1715,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>30.28271293640137</v>
+        <v>30.28271484375</v>
       </c>
       <c r="C61" t="n">
         <v>51.91375732421875</v>
@@ -1740,7 +1740,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>31.77685356140137</v>
+        <v>31.77684211730957</v>
       </c>
       <c r="C62" t="n">
         <v>54.47513961791992</v>
@@ -1794,7 +1794,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>35.8276481628418</v>
+        <v>35.82765579223633</v>
       </c>
       <c r="C64" t="n">
         <v>60.87860107421875</v>
@@ -1823,7 +1823,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>35.39247894287109</v>
+        <v>35.39248275756836</v>
       </c>
       <c r="C65" t="n">
         <v>60.13915252685547</v>
@@ -1852,7 +1852,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>33.14921951293945</v>
+        <v>33.14922332763672</v>
       </c>
       <c r="C66" t="n">
         <v>55.81681823730469</v>
@@ -1881,7 +1881,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>34.04111480712891</v>
+        <v>34.04112243652344</v>
       </c>
       <c r="C67" t="n">
         <v>57.31858062744141</v>
@@ -1910,7 +1910,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>32.88129043579102</v>
+        <v>32.88128662109375</v>
       </c>
       <c r="C68" t="n">
         <v>54.87916946411133</v>
@@ -1939,7 +1939,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>31.09083938598633</v>
+        <v>31.09084510803223</v>
       </c>
       <c r="C69" t="n">
         <v>51.89088821411133</v>
@@ -1968,7 +1968,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>28.92128372192383</v>
+        <v>28.92129707336426</v>
       </c>
       <c r="C70" t="n">
         <v>48.26988220214844</v>
@@ -2026,7 +2026,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>32.89525604248047</v>
+        <v>32.89526748657227</v>
       </c>
       <c r="C72" t="n">
         <v>54.36841583251953</v>
@@ -2142,7 +2142,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>35.37633514404297</v>
+        <v>35.37632369995117</v>
       </c>
       <c r="C76" t="n">
         <v>57.94368362426758</v>
@@ -2171,7 +2171,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>33.33781433105469</v>
+        <v>33.33780670166016</v>
       </c>
       <c r="C77" t="n">
         <v>54.604736328125</v>
@@ -2200,7 +2200,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>32.2520637512207</v>
+        <v>32.25207138061523</v>
       </c>
       <c r="C78" t="n">
         <v>52.15999984741211</v>
@@ -2229,7 +2229,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>34.55226898193359</v>
+        <v>34.55226516723633</v>
       </c>
       <c r="C79" t="n">
         <v>55.88000106811523</v>
@@ -2258,7 +2258,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>34.05781173706055</v>
+        <v>34.05780792236328</v>
       </c>
       <c r="C80" t="n">
         <v>54.43999862670898</v>
@@ -2287,7 +2287,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>35.52798461914062</v>
+        <v>35.52798080444336</v>
       </c>
       <c r="C81" t="n">
         <v>56.79000091552734</v>
@@ -2316,7 +2316,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>35.77195739746094</v>
+        <v>35.7719612121582</v>
       </c>
       <c r="C82" t="n">
         <v>57.18000030517578</v>
@@ -2345,7 +2345,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>36.61328506469727</v>
+        <v>36.61328887939453</v>
       </c>
       <c r="C83" t="n">
         <v>57.84999847412109</v>
@@ -2374,7 +2374,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>36.0373420715332</v>
+        <v>36.03734970092773</v>
       </c>
       <c r="C84" t="n">
         <v>56.93999862670898</v>
@@ -2403,7 +2403,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>36.70188522338867</v>
+        <v>36.70188903808594</v>
       </c>
       <c r="C85" t="n">
         <v>57.9900016784668</v>
@@ -2432,7 +2432,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>36.70822143554688</v>
+        <v>36.70822906494141</v>
       </c>
       <c r="C86" t="n">
         <v>58</v>
@@ -2461,7 +2461,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>37.09428787231445</v>
+        <v>37.09429168701172</v>
       </c>
       <c r="C87" t="n">
         <v>57.95000076293945</v>
@@ -2490,7 +2490,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>38.47051620483398</v>
+        <v>38.47051239013672</v>
       </c>
       <c r="C88" t="n">
         <v>60.09999847412109</v>
@@ -2519,7 +2519,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>38.6945686340332</v>
+        <v>38.69457626342773</v>
       </c>
       <c r="C89" t="n">
         <v>60.45000076293945</v>
@@ -2548,7 +2548,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>39.67140197753906</v>
+        <v>39.6713981628418</v>
       </c>
       <c r="C90" t="n">
         <v>61.34000015258789</v>
@@ -2606,7 +2606,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>42.39413452148438</v>
+        <v>42.39412689208984</v>
       </c>
       <c r="C92" t="n">
         <v>64.86000061035156</v>
@@ -2635,7 +2635,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>43.33535385131836</v>
+        <v>43.33535003662109</v>
       </c>
       <c r="C93" t="n">
         <v>66.30000305175781</v>
@@ -2664,7 +2664,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>45.43349075317383</v>
+        <v>45.43347930908203</v>
       </c>
       <c r="C94" t="n">
         <v>69.51000213623047</v>
@@ -2722,7 +2722,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>48.0591926574707</v>
+        <v>48.05921173095703</v>
       </c>
       <c r="C96" t="n">
         <v>72.80000305175781</v>
@@ -2751,7 +2751,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>46.63987731933594</v>
+        <v>46.63986587524414</v>
       </c>
       <c r="C97" t="n">
         <v>70.65000152587891</v>
@@ -2780,7 +2780,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>42.87699127197266</v>
+        <v>42.87700653076172</v>
       </c>
       <c r="C98" t="n">
         <v>64.94999694824219</v>
@@ -2809,7 +2809,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>44.36965179443359</v>
+        <v>44.3696403503418</v>
       </c>
       <c r="C99" t="n">
         <v>66.5</v>
@@ -2838,7 +2838,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>46.93841934204102</v>
+        <v>46.93841171264648</v>
       </c>
       <c r="C100" t="n">
         <v>70.34999847412109</v>
@@ -2867,7 +2867,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>49.58058166503906</v>
+        <v>49.58058547973633</v>
       </c>
       <c r="C101" t="n">
         <v>74.30999755859375</v>
@@ -2896,7 +2896,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>53.80974197387695</v>
+        <v>53.80972290039062</v>
       </c>
       <c r="C102" t="n">
         <v>79.94000244140625</v>
@@ -2925,7 +2925,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>57.70710372924805</v>
+        <v>57.70713806152344</v>
       </c>
       <c r="C103" t="n">
         <v>85.73000335693359</v>
@@ -2954,7 +2954,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>56.0045166015625</v>
+        <v>56.00453186035156</v>
       </c>
       <c r="C104" t="n">
         <v>82.5</v>
@@ -2983,7 +2983,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>55.13560104370117</v>
+        <v>55.13562393188477</v>
       </c>
       <c r="C105" t="n">
         <v>81.22000122070312</v>
@@ -3012,7 +3012,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>51.94506072998047</v>
+        <v>51.94504165649414</v>
       </c>
       <c r="C106" t="n">
         <v>76.51999664306641</v>
@@ -3041,7 +3041,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>49.46298599243164</v>
+        <v>49.46299362182617</v>
       </c>
       <c r="C107" t="n">
         <v>72.15000152587891</v>
@@ -3070,7 +3070,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>45.29479217529297</v>
+        <v>45.2947883605957</v>
       </c>
       <c r="C108" t="n">
         <v>66.06999969482422</v>
@@ -3099,7 +3099,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>47.34460067749023</v>
+        <v>47.34461212158203</v>
       </c>
       <c r="C109" t="n">
         <v>69.05999755859375</v>
@@ -3128,7 +3128,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>43.17642211914062</v>
+        <v>43.17641067504883</v>
       </c>
       <c r="C110" t="n">
         <v>62.97999954223633</v>
@@ -3157,7 +3157,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>45.18427658081055</v>
+        <v>45.18428421020508</v>
       </c>
       <c r="C111" t="n">
         <v>65.19999694824219</v>
@@ -3186,7 +3186,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>43.14683151245117</v>
+        <v>43.14682388305664</v>
       </c>
       <c r="C112" t="n">
         <v>62.2599983215332</v>
@@ -3215,7 +3215,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>47.06927871704102</v>
+        <v>47.06925964355469</v>
       </c>
       <c r="C113" t="n">
         <v>67.91999816894531</v>
@@ -3244,7 +3244,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>44.63121032714844</v>
+        <v>44.63123321533203</v>
       </c>
       <c r="C114" t="n">
         <v>63.68000030517578</v>
@@ -3273,7 +3273,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>43.04025650024414</v>
+        <v>43.04026031494141</v>
       </c>
       <c r="C115" t="n">
         <v>61.40999984741211</v>
@@ -3302,7 +3302,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>35.75557327270508</v>
+        <v>35.75558090209961</v>
       </c>
       <c r="C116" t="n">
         <v>50.34000015258789</v>
@@ -3331,7 +3331,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>34.91033554077148</v>
+        <v>34.91034698486328</v>
       </c>
       <c r="C117" t="n">
         <v>49.15000152587891</v>
@@ -3360,7 +3360,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>34.06510543823242</v>
+        <v>34.06511306762695</v>
       </c>
       <c r="C118" t="n">
         <v>47.95999908447266</v>
@@ -3389,7 +3389,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>38.40596771240234</v>
+        <v>38.40597152709961</v>
       </c>
       <c r="C119" t="n">
         <v>53.34999847412109</v>
@@ -3418,7 +3418,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>38.90990829467773</v>
+        <v>38.90989685058594</v>
       </c>
       <c r="C120" t="n">
         <v>54.04999923706055</v>
@@ -3445,7 +3445,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>33.61152648925781</v>
+        <v>33.61152267456055</v>
       </c>
       <c r="C121" t="n">
         <v>46.68999862670898</v>
@@ -3472,7 +3472,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>28.13318634033203</v>
+        <v>28.13319396972656</v>
       </c>
       <c r="C122" t="n">
         <v>39.08000183105469</v>
@@ -3499,7 +3499,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>24.54351806640625</v>
+        <v>24.54351615905762</v>
       </c>
       <c r="C123" t="n">
         <v>33.83000183105469</v>
@@ -3526,7 +3526,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>29.21570777893066</v>
+        <v>29.21570014953613</v>
       </c>
       <c r="C124" t="n">
         <v>40.27000045776367</v>
@@ -3553,7 +3553,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>34.67142868041992</v>
+        <v>34.67144012451172</v>
       </c>
       <c r="C125" t="n">
         <v>47.79000091552734</v>
@@ -3580,7 +3580,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>31.95190238952637</v>
+        <v>31.9518928527832</v>
       </c>
       <c r="C126" t="n">
         <v>43.79000091552734</v>
@@ -3607,7 +3607,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>31.81328010559082</v>
+        <v>31.81326484680176</v>
       </c>
       <c r="C127" t="n">
         <v>43.59999847412109</v>
@@ -3634,7 +3634,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>29.96303749084473</v>
+        <v>29.96303558349609</v>
       </c>
       <c r="C128" t="n">
         <v>40.81999969482422</v>
@@ -3661,7 +3661,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>30.13186264038086</v>
+        <v>30.1318531036377</v>
       </c>
       <c r="C129" t="n">
         <v>41.04999923706055</v>
@@ -3688,7 +3688,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>31.90821266174316</v>
+        <v>31.90819549560547</v>
       </c>
       <c r="C130" t="n">
         <v>43.47000122070312</v>
@@ -3715,7 +3715,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>32.07800674438477</v>
+        <v>32.0780029296875</v>
       </c>
       <c r="C131" t="n">
         <v>43.45000076293945</v>
@@ -3769,7 +3769,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>37.01705932617188</v>
+        <v>37.01706314086914</v>
       </c>
       <c r="C133" t="n">
         <v>50.13999938964844</v>
@@ -3796,7 +3796,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>35.99823760986328</v>
+        <v>35.99824142456055</v>
       </c>
       <c r="C134" t="n">
         <v>48.7599983215332</v>
@@ -3823,7 +3823,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>35.30754089355469</v>
+        <v>35.30753326416016</v>
       </c>
       <c r="C135" t="n">
         <v>47.56999969482422</v>
@@ -3877,7 +3877,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>35.55989456176758</v>
+        <v>35.55989074707031</v>
       </c>
       <c r="C137" t="n">
         <v>47.90999984741211</v>
@@ -3904,7 +3904,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>33.35560989379883</v>
+        <v>33.35559844970703</v>
       </c>
       <c r="C138" t="n">
         <v>44.68999862670898</v>
@@ -3931,7 +3931,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>32.81072998046875</v>
+        <v>32.81076049804688</v>
       </c>
       <c r="C139" t="n">
         <v>43.95999908447266</v>
@@ -3958,7 +3958,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>34.06991958618164</v>
+        <v>34.06992340087891</v>
       </c>
       <c r="C140" t="n">
         <v>45.36999893188477</v>
@@ -4012,7 +4012,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>37.58430862426758</v>
+        <v>37.58429336547852</v>
       </c>
       <c r="C142" t="n">
         <v>50.04999923706055</v>
@@ -4039,7 +4039,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>38.61577606201172</v>
+        <v>38.61576461791992</v>
       </c>
       <c r="C143" t="n">
         <v>51.15000152587891</v>
@@ -4093,7 +4093,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>41.43928909301758</v>
+        <v>41.43929290771484</v>
       </c>
       <c r="C145" t="n">
         <v>54.88999938964844</v>
@@ -4147,7 +4147,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>41.22208786010742</v>
+        <v>41.22208023071289</v>
       </c>
       <c r="C147" t="n">
         <v>54.31000137329102</v>
@@ -4174,7 +4174,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>45.00196838378906</v>
+        <v>45.00197982788086</v>
       </c>
       <c r="C148" t="n">
         <v>59.29000091552734</v>
@@ -4201,7 +4201,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>49.71545028686523</v>
+        <v>49.71545791625977</v>
       </c>
       <c r="C149" t="n">
         <v>65.5</v>
@@ -4255,7 +4255,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>53.06067276000977</v>
+        <v>53.06069564819336</v>
       </c>
       <c r="C151" t="n">
         <v>69.62000274658203</v>
@@ -4282,7 +4282,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>55.23001098632812</v>
+        <v>55.23004150390625</v>
       </c>
       <c r="C152" t="n">
         <v>72.16999816894531</v>
@@ -4309,7 +4309,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>56.19426727294922</v>
+        <v>56.19426345825195</v>
       </c>
       <c r="C153" t="n">
         <v>73.43000030517578</v>
@@ -4338,7 +4338,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>59.23242950439453</v>
+        <v>59.23239898681641</v>
       </c>
       <c r="C154" t="n">
         <v>77.40000152587891</v>
@@ -4367,7 +4367,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>53.71792221069336</v>
+        <v>53.71793365478516</v>
       </c>
       <c r="C155" t="n">
         <v>69.90000152587891</v>
@@ -4396,7 +4396,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>50.85912322998047</v>
+        <v>50.85913848876953</v>
       </c>
       <c r="C156" t="n">
         <v>66.18000030517578</v>
@@ -4454,7 +4454,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>52.01955413818359</v>
+        <v>52.01956558227539</v>
       </c>
       <c r="C158" t="n">
         <v>67.69000244140625</v>
@@ -4483,7 +4483,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>52.37925720214844</v>
+        <v>52.37926483154297</v>
       </c>
       <c r="C159" t="n">
         <v>67.84999847412109</v>
@@ -4512,7 +4512,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>51.52235794067383</v>
+        <v>51.52235412597656</v>
       </c>
       <c r="C160" t="n">
         <v>66.73999786376953</v>
@@ -4541,7 +4541,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>48.72776031494141</v>
+        <v>48.72776794433594</v>
       </c>
       <c r="C161" t="n">
         <v>63.11999893188477</v>
@@ -4570,7 +4570,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>45.74301528930664</v>
+        <v>45.74301147460938</v>
       </c>
       <c r="C162" t="n">
         <v>58.95999908447266</v>
@@ -4628,7 +4628,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>46.06905364990234</v>
+        <v>46.06906509399414</v>
       </c>
       <c r="C164" t="n">
         <v>59.08000183105469</v>
@@ -4657,7 +4657,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>40.68862152099609</v>
+        <v>40.68861770629883</v>
       </c>
       <c r="C165" t="n">
         <v>52.18000030517578</v>
@@ -4715,7 +4715,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>43.36909484863281</v>
+        <v>43.36909103393555</v>
       </c>
       <c r="C167" t="n">
         <v>55.20000076293945</v>
@@ -4744,7 +4744,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>47.09318161010742</v>
+        <v>47.09317779541016</v>
       </c>
       <c r="C168" t="n">
         <v>59.93999862670898</v>
@@ -4773,7 +4773,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>51.09225082397461</v>
+        <v>51.09223556518555</v>
       </c>
       <c r="C169" t="n">
         <v>65.02999877929688</v>
@@ -4802,7 +4802,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>46.69248580932617</v>
+        <v>46.69248199462891</v>
       </c>
       <c r="C170" t="n">
         <v>59.43000030517578</v>
@@ -4831,7 +4831,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>38.31148910522461</v>
+        <v>38.31150054931641</v>
       </c>
       <c r="C171" t="n">
         <v>48.41999816894531</v>
@@ -4860,7 +4860,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>24.36997032165527</v>
+        <v>24.36997604370117</v>
       </c>
       <c r="C172" t="n">
         <v>30.79999923706055</v>
@@ -4918,7 +4918,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>33.70795059204102</v>
+        <v>33.70795440673828</v>
       </c>
       <c r="C174" t="n">
         <v>42.18000030517578</v>
@@ -4972,7 +4972,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>30.18486404418945</v>
+        <v>30.18485069274902</v>
       </c>
       <c r="C176" t="n">
         <v>37.38999938964844</v>
@@ -4997,7 +4997,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>30.58851051330566</v>
+        <v>30.5885066986084</v>
       </c>
       <c r="C177" t="n">
         <v>37.88999938964844</v>
@@ -5022,7 +5022,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>26.51165771484375</v>
+        <v>26.51166152954102</v>
       </c>
       <c r="C178" t="n">
         <v>32.84000015258789</v>
@@ -5072,7 +5072,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>32.32940673828125</v>
+        <v>32.32939529418945</v>
       </c>
       <c r="C180" t="n">
         <v>39.56000137329102</v>
@@ -5097,7 +5097,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>32.68081283569336</v>
+        <v>32.6807975769043</v>
       </c>
       <c r="C181" t="n">
         <v>39.9900016784668</v>
@@ -5147,7 +5147,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>42.89419937133789</v>
+        <v>42.89420318603516</v>
       </c>
       <c r="C183" t="n">
         <v>52.0099983215332</v>
@@ -5172,7 +5172,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>43.68595123291016</v>
+        <v>43.68594741821289</v>
       </c>
       <c r="C184" t="n">
         <v>52.97000122070312</v>
@@ -5197,7 +5197,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>42.17669677734375</v>
+        <v>42.17668914794922</v>
       </c>
       <c r="C185" t="n">
         <v>51.13999938964844</v>
@@ -5222,7 +5222,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>46.32815933227539</v>
+        <v>46.32815551757812</v>
       </c>
       <c r="C186" t="n">
         <v>55.7400016784668</v>
@@ -5247,7 +5247,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>50.61688613891602</v>
+        <v>50.61688232421875</v>
       </c>
       <c r="C187" t="n">
         <v>60.90000152587891</v>
@@ -5272,7 +5272,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>46.95037460327148</v>
+        <v>46.95038604736328</v>
       </c>
       <c r="C188" t="n">
         <v>56.06000137329102</v>
@@ -5297,7 +5297,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>46.50650787353516</v>
+        <v>46.50649642944336</v>
       </c>
       <c r="C189" t="n">
         <v>55.52999877929688</v>
@@ -5372,7 +5372,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>59.08689117431641</v>
+        <v>59.08687591552734</v>
       </c>
       <c r="C192" t="n">
         <v>70.12999725341797</v>
@@ -5397,7 +5397,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>60.98282241821289</v>
+        <v>60.98283004760742</v>
       </c>
       <c r="C193" t="n">
         <v>72.18000030517578</v>
@@ -5422,7 +5422,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>74.87249755859375</v>
+        <v>74.87248992919922</v>
       </c>
       <c r="C194" t="n">
         <v>88.62000274658203</v>
@@ -5476,7 +5476,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>85.16584777832031</v>
+        <v>85.16585540771484</v>
       </c>
       <c r="C196" t="n">
         <v>100</v>
@@ -5505,7 +5505,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>81.35042572021484</v>
+        <v>81.35043334960938</v>
       </c>
       <c r="C197" t="n">
         <v>95.51999664306641</v>
@@ -5534,7 +5534,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>96.12200927734375</v>
+        <v>96.12201690673828</v>
       </c>
       <c r="C198" t="n">
         <v>112.3600006103516</v>
@@ -5679,7 +5679,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>110.7638244628906</v>
+        <v>110.7638168334961</v>
       </c>
       <c r="C203" t="n">
         <v>126.0899963378906</v>
@@ -5708,7 +5708,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>108.9120635986328</v>
+        <v>108.9120712280273</v>
       </c>
       <c r="C204" t="n">
         <v>123.5100021362305</v>
@@ -5737,7 +5737,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>104.7024993896484</v>
+        <v>104.7024688720703</v>
       </c>
       <c r="C205" t="n">
         <v>118</v>
@@ -5766,7 +5766,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>108.1363906860352</v>
+        <v>108.1363754272461</v>
       </c>
       <c r="C206" t="n">
         <v>121.870002746582</v>
@@ -5795,7 +5795,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>92.11167144775391</v>
+        <v>92.1116943359375</v>
       </c>
       <c r="C207" t="n">
         <v>103.3499984741211</v>
@@ -5853,7 +5853,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>92.26963043212891</v>
+        <v>92.26963806152344</v>
       </c>
       <c r="C209" t="n">
         <v>102.8899993896484</v>
@@ -5882,7 +5882,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>89.50932312011719</v>
+        <v>89.50931549072266</v>
       </c>
       <c r="C210" t="n">
         <v>99.30000305175781</v>
@@ -5911,7 +5911,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>93.95552062988281</v>
+        <v>93.95552825927734</v>
       </c>
       <c r="C211" t="n">
         <v>103.6100006103516</v>
@@ -5940,7 +5940,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>106.7507247924805</v>
+        <v>106.7507400512695</v>
       </c>
       <c r="C212" t="n">
         <v>117.7200012207031</v>
@@ -5969,7 +5969,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>108.4084548950195</v>
+        <v>108.408447265625</v>
       </c>
       <c r="C213" t="n">
         <v>119.0299987792969</v>
@@ -5998,7 +5998,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>109.6573715209961</v>
+        <v>109.6573867797852</v>
       </c>
       <c r="C214" t="n">
         <v>119.8000030517578</v>
@@ -6027,7 +6027,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>108.7420501708984</v>
+        <v>108.7420349121094</v>
       </c>
       <c r="C215" t="n">
         <v>118.8000030517578</v>
@@ -6085,7 +6085,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>106.7788696289062</v>
+        <v>106.7788619995117</v>
       </c>
       <c r="C217" t="n">
         <v>116.0699996948242</v>
@@ -6143,7 +6143,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>104.2699890136719</v>
+        <v>104.2699966430664</v>
       </c>
       <c r="C219" t="n">
         <v>112.5400009155273</v>
@@ -6201,7 +6201,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>116.388801574707</v>
+        <v>116.3888092041016</v>
       </c>
       <c r="C221" t="n">
         <v>125.620002746582</v>
@@ -6259,7 +6259,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>106.6489486694336</v>
+        <v>106.6489562988281</v>
       </c>
       <c r="C223" t="n">
         <v>114.379997253418</v>
@@ -6288,7 +6288,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>103.6838912963867</v>
+        <v>103.6838989257812</v>
       </c>
       <c r="C224" t="n">
         <v>111.1999969482422</v>
@@ -6317,7 +6317,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>106.8663177490234</v>
+        <v>106.8663101196289</v>
       </c>
       <c r="C225" t="n">
         <v>113.7900009155273</v>
@@ -6375,7 +6375,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>102.8749160766602</v>
+        <v>102.8749008178711</v>
       </c>
       <c r="C227" t="n">
         <v>109.5400009155273</v>
@@ -6404,7 +6404,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>102.4589385986328</v>
+        <v>102.4589309692383</v>
       </c>
       <c r="C228" t="n">
         <v>108.3399963378906</v>
@@ -6491,7 +6491,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>94.52871704101562</v>
+        <v>94.52872467041016</v>
       </c>
       <c r="C231" t="n">
         <v>99.15000152587891</v>
@@ -6520,7 +6520,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>100.1251220703125</v>
+        <v>100.125129699707</v>
       </c>
       <c r="C232" t="n">
         <v>105.0199966430664</v>
@@ -6549,7 +6549,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>84.96620178222656</v>
+        <v>84.96620941162109</v>
       </c>
       <c r="C233" t="n">
         <v>89.12000274658203</v>
@@ -6607,7 +6607,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>86.28545379638672</v>
+        <v>86.28546142578125</v>
       </c>
       <c r="C235" t="n">
         <v>89.73999786376953</v>
@@ -6694,7 +6694,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>91.69905090332031</v>
+        <v>91.69904327392578</v>
       </c>
       <c r="C238" t="n">
         <v>94.58999633789062</v>
@@ -6810,7 +6810,7 @@
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>101.9819793701172</v>
+        <v>101.9819869995117</v>
       </c>
       <c r="C242" t="n">
         <v>104.2300033569336</v>
@@ -6897,7 +6897,7 @@
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>124.0249176025391</v>
+        <v>124.0249099731445</v>
       </c>
       <c r="C245" t="n">
         <v>125.7799987792969</v>
